--- a/plans/bar-equipment.xlsx
+++ b/plans/bar-equipment.xlsx
@@ -498,7 +498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bar equipment · Betalbatim pub</t>
+          <t>Bar equipment · Cabin East, Betalbatim</t>
         </is>
       </c>
     </row>
